--- a/esyluban/examples/release/DataTables/test/define_from_excel_one.xlsx
+++ b/esyluban/examples/release/DataTables/test/define_from_excel_one.xlsx
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12380952380952" defaultRowHeight="15"/>
   <cols>
     <col width="13.752380952381" customWidth="1" style="2" min="1" max="1"/>
@@ -1172,11 +1172,12 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
